--- a/tests/data/export/xlsx/span-target/doc1.xlsx
+++ b/tests/data/export/xlsx/span-target/doc1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>a</t>
     <phoneticPr fontId="1"/>
@@ -25,11 +25,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>number</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>Another</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>An</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -91,9 +99,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="1" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -362,58 +371,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="8.38" customWidth="1"/>
+    <col min="1" max="3" width="8.38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s" s="2">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="C1" t="s" s="2">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s" s="2">
         <v>3</v>
       </c>
+      <c r="B2" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" spans="2:2">
-      <c r="B3" t="s">
-        <v>4</v>
+      <c r="B3" t="s" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
+      <c r="A4" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>7</v>
+      <c r="A5" t="s" s="2">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>8</v>
+      <c r="A6" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C2:C3"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -429,11 +445,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" t="s">
-        <v>10</v>
+      <c r="A1" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s" s="2">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
